--- a/src/main/resources/excel_data/ConveyorUpload.xlsx
+++ b/src/main/resources/excel_data/ConveyorUpload.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10312"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10211"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65708513-27AB-614E-99CE-A0C98F3705D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A84D5B-B33F-7A44-BEEA-1F41BBED170A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1252,13 +1252,13 @@
     <t>Mechanical</t>
   </si>
   <si>
+    <t>Dual drive 381</t>
+  </si>
+  <si>
+    <t>5,3,3</t>
+  </si>
+  <si>
     <t>601</t>
-  </si>
-  <si>
-    <t>Dual drive 381</t>
-  </si>
-  <si>
-    <t>5,3,3</t>
   </si>
   <si>
     <t>2.6</t>
@@ -1651,6 +1651,7 @@
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="28" max="28" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -1982,7 +1983,7 @@
         <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D4">
         <v>23</v>
@@ -2003,7 +2004,7 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K4">
         <v>24</v>
@@ -2024,7 +2025,7 @@
         <v>144</v>
       </c>
       <c r="Q4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R4" t="s">
         <v>147</v>

--- a/src/main/resources/excel_data/ConveyorUpload.xlsx
+++ b/src/main/resources/excel_data/ConveyorUpload.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A84D5B-B33F-7A44-BEEA-1F41BBED170A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED27410-F2C7-4679-B727-F2E20A9B4683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cust Automation Sanity Site Aus" sheetId="1" r:id="rId1"/>
@@ -1147,12 +1147,6 @@
     <t>Bare</t>
   </si>
   <si>
-    <t>C7 Automation Sanity</t>
-  </si>
-  <si>
-    <t>C8 Automation Sanity</t>
-  </si>
-  <si>
     <t>eg. Conveyor Name</t>
   </si>
   <si>
@@ -1262,6 +1256,12 @@
   </si>
   <si>
     <t>2.6</t>
+  </si>
+  <si>
+    <t>C9 Automation Sanity</t>
+  </si>
+  <si>
+    <t>C10 Automation Sanity</t>
   </si>
 </sst>
 </file>
@@ -1647,14 +1647,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="28" max="28" width="11.1640625" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1761,116 +1761,116 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C2" t="s">
         <v>374</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>375</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>376</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>377</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>378</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>379</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>380</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>381</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>382</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>383</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>384</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>385</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>386</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>387</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>388</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>389</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>390</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>391</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
+        <v>391</v>
+      </c>
+      <c r="V2" t="s">
         <v>392</v>
       </c>
-      <c r="T2" t="s">
+      <c r="W2" t="s">
         <v>393</v>
       </c>
-      <c r="U2" t="s">
+      <c r="X2" t="s">
         <v>393</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Y2" t="s">
         <v>394</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Z2" t="s">
+        <v>394</v>
+      </c>
+      <c r="AA2" t="s">
         <v>395</v>
       </c>
-      <c r="X2" t="s">
-        <v>395</v>
-      </c>
-      <c r="Y2" t="s">
+      <c r="AB2" t="s">
         <v>396</v>
       </c>
-      <c r="Z2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>397</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>398</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
+        <v>398</v>
+      </c>
+      <c r="AF2" t="s">
         <v>399</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AG2" t="s">
         <v>400</v>
       </c>
-      <c r="AE2" t="s">
-        <v>400</v>
-      </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>401</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>402</v>
       </c>
-      <c r="AH2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>372</v>
+        <v>409</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
@@ -1918,7 +1918,7 @@
         <v>144</v>
       </c>
       <c r="Q3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="R3" t="s">
         <v>147</v>
@@ -1966,7 +1966,7 @@
         <v>23</v>
       </c>
       <c r="AG3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AH3">
         <v>3</v>
@@ -1975,15 +1975,15 @@
         <v>44920</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="B4" t="s">
         <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D4">
         <v>23</v>
@@ -2004,7 +2004,7 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="K4">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>144</v>
       </c>
       <c r="Q4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="R4" t="s">
         <v>147</v>
@@ -2064,7 +2064,7 @@
         <v>23</v>
       </c>
       <c r="AD4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AE4" t="s">
         <v>351</v>
@@ -2073,7 +2073,7 @@
         <v>24</v>
       </c>
       <c r="AG4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AH4">
         <v>4</v>
@@ -2279,79 +2279,79 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:A15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>178</v>
       </c>
@@ -2365,629 +2365,629 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:A125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>303</v>
       </c>
@@ -3001,629 +3001,629 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:A125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>303</v>
       </c>
@@ -3637,294 +3637,294 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:A58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>361</v>
       </c>
@@ -3938,294 +3938,294 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:A58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>361</v>
       </c>
@@ -4239,44 +4239,44 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>369</v>
       </c>
@@ -4290,39 +4290,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -4336,94 +4336,94 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -4437,314 +4437,314 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>121</v>
       </c>
@@ -4758,59 +4758,59 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>132</v>
       </c>
@@ -4824,34 +4824,34 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>138</v>
       </c>
@@ -4865,24 +4865,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -4896,19 +4896,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>145</v>
       </c>
@@ -4922,99 +4922,99 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>163</v>
       </c>

--- a/src/main/resources/excel_data/ConveyorUpload.xlsx
+++ b/src/main/resources/excel_data/ConveyorUpload.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A84D5B-B33F-7A44-BEEA-1F41BBED170A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3931DE-5336-45F5-AB09-94404F542FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cust Automation Sanity Site Aus" sheetId="1" r:id="rId1"/>
@@ -1647,14 +1647,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="28" max="28" width="11.1640625" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" customWidth="1"/>
+    <col min="35" max="35" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1761,7 +1762,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>374</v>
       </c>
@@ -1868,7 +1869,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>372</v>
       </c>
@@ -1975,7 +1976,7 @@
         <v>44920</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>373</v>
       </c>
@@ -2279,79 +2280,79 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:A15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>178</v>
       </c>
@@ -2365,629 +2366,629 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:A125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>303</v>
       </c>
@@ -3001,629 +3002,629 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:A125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>303</v>
       </c>
@@ -3637,294 +3638,294 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:A58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>361</v>
       </c>
@@ -3938,294 +3939,294 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:A58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>361</v>
       </c>
@@ -4239,44 +4240,44 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>369</v>
       </c>
@@ -4290,39 +4291,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -4336,94 +4337,94 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -4437,314 +4438,314 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>121</v>
       </c>
@@ -4758,59 +4759,59 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>132</v>
       </c>
@@ -4824,34 +4825,34 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>138</v>
       </c>
@@ -4865,24 +4866,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -4896,19 +4897,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>145</v>
       </c>
@@ -4922,99 +4923,99 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>163</v>
       </c>

--- a/src/main/resources/excel_data/ConveyorUpload.xlsx
+++ b/src/main/resources/excel_data/ConveyorUpload.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED27410-F2C7-4679-B727-F2E20A9B4683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07B74B4-4F99-4F29-885B-20BBD89C1C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1258,10 +1258,10 @@
     <t>2.6</t>
   </si>
   <si>
-    <t>C9 Automation Sanity</t>
-  </si>
-  <si>
-    <t>C10 Automation Sanity</t>
+    <t>C7 Automation Sanity</t>
+  </si>
+  <si>
+    <t>C8 Automation Sanity</t>
   </si>
 </sst>
 </file>
